--- a/docs/manuscript/threshold_price.xlsx
+++ b/docs/manuscript/threshold_price.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\HPRU\Shingrix\HPRU_RZV\docs\manuscript\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HPRU_RZV\docs\manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{48281D21-91C7-4E70-A066-8DDCE72D8C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A91852-390D-477D-BB40-C6282B577CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9DFA8D53-1391-44E8-8854-98FB93BA3912}"/>
+    <workbookView xWindow="7860" yWindow="2370" windowWidth="40365" windowHeight="17910" xr2:uid="{9DFA8D53-1391-44E8-8854-98FB93BA3912}"/>
   </bookViews>
   <sheets>
     <sheet name="threshold_price" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="16">
   <si>
     <t>Age</t>
   </si>
@@ -47,6 +60,27 @@
   </si>
   <si>
     <t>ZVL at 70 years old</t>
+  </si>
+  <si>
+    <t>Age0</t>
+  </si>
+  <si>
+    <t>Arm</t>
+  </si>
+  <si>
+    <t>Reg2d</t>
+  </si>
+  <si>
+    <t>Reg1d</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>RZV</t>
+  </si>
+  <si>
+    <t>ReRZV</t>
   </si>
 </sst>
 </file>
@@ -582,19 +616,7 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -608,6 +630,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -985,272 +1019,515 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CAF610C-73B4-40CF-84A9-10A3EB4A55A5}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="25.5703125" style="7" customWidth="1"/>
+    <col min="1" max="6" width="25.5703125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
-    <row r="2" spans="1:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="8" t="s">
+    <row r="2" spans="1:15" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="K2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="19.5" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+    <row r="3" spans="1:15" ht="19.5" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>60</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="9">
-        <v>109.097455004758</v>
-      </c>
-      <c r="D3" s="9">
-        <v>218.19491000951601</v>
-      </c>
-      <c r="E3" s="9">
-        <v>189.304364947973</v>
-      </c>
-      <c r="F3" s="9">
-        <v>28.8905450615426</v>
+      <c r="C3" s="5">
+        <f>N3</f>
+        <v>108.656886342448</v>
+      </c>
+      <c r="D3" s="5">
+        <f>2*C3</f>
+        <v>217.31377268489601</v>
+      </c>
+      <c r="E3" s="5">
+        <f>O3</f>
+        <v>192.897349376102</v>
+      </c>
+      <c r="F3" s="5">
+        <f>D3-E3</f>
+        <v>24.416423308794009</v>
+      </c>
+      <c r="K3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3">
+        <v>60</v>
+      </c>
+      <c r="M3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3">
+        <v>108.656886342448</v>
+      </c>
+      <c r="O3">
+        <v>192.897349376102</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>65</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="10">
-        <v>113.335604773459</v>
-      </c>
-      <c r="D4" s="10">
-        <v>226.67120954691799</v>
-      </c>
-      <c r="E4" s="10">
-        <v>197.23105302898</v>
-      </c>
-      <c r="F4" s="10">
-        <v>29.440156517938199</v>
+      <c r="C4" s="6">
+        <f t="shared" ref="C4:C14" si="0">N4</f>
+        <v>113.100632652073</v>
+      </c>
+      <c r="D4" s="6">
+        <f t="shared" ref="D4:D14" si="1">2*C4</f>
+        <v>226.20126530414601</v>
+      </c>
+      <c r="E4" s="6">
+        <f t="shared" ref="E4:E14" si="2">O4</f>
+        <v>200.76575391086899</v>
+      </c>
+      <c r="F4" s="6">
+        <f t="shared" ref="F4:F14" si="3">D4-E4</f>
+        <v>25.435511393277011</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4">
+        <v>65</v>
+      </c>
+      <c r="M4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4">
+        <v>113.100632652073</v>
+      </c>
+      <c r="O4">
+        <v>200.76575391086899</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>70</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="10">
-        <v>113.537531758146</v>
-      </c>
-      <c r="D5" s="10">
-        <v>227.075063516292</v>
-      </c>
-      <c r="E5" s="10">
-        <v>198.23524880493099</v>
-      </c>
-      <c r="F5" s="10">
-        <v>28.839814711360699</v>
+      <c r="C5" s="6">
+        <f t="shared" si="0"/>
+        <v>113.384703877767</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" si="1"/>
+        <v>226.76940775553399</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" si="2"/>
+        <v>201.88375360209801</v>
+      </c>
+      <c r="F5" s="6">
+        <f t="shared" si="3"/>
+        <v>24.885654153435979</v>
+      </c>
+      <c r="K5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5">
+        <v>70</v>
+      </c>
+      <c r="M5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5">
+        <v>113.384703877767</v>
+      </c>
+      <c r="O5">
+        <v>201.88375360209801</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>75</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="10">
-        <v>107.95349401287601</v>
-      </c>
-      <c r="D6" s="10">
-        <v>215.90698802575301</v>
-      </c>
-      <c r="E6" s="10">
-        <v>188.335092787946</v>
-      </c>
-      <c r="F6" s="10">
-        <v>27.571895237806899</v>
+      <c r="C6" s="6">
+        <f t="shared" si="0"/>
+        <v>107.807521956225</v>
+      </c>
+      <c r="D6" s="6">
+        <f t="shared" si="1"/>
+        <v>215.61504391245001</v>
+      </c>
+      <c r="E6" s="6">
+        <f t="shared" si="2"/>
+        <v>191.84932966330001</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" si="3"/>
+        <v>23.765714249149994</v>
+      </c>
+      <c r="K6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6">
+        <v>75</v>
+      </c>
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6">
+        <v>107.807521956225</v>
+      </c>
+      <c r="O6">
+        <v>191.84932966330001</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
         <v>80</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="10">
-        <v>95.792798999108498</v>
-      </c>
-      <c r="D7" s="10">
-        <v>191.585597998217</v>
-      </c>
-      <c r="E7" s="10">
-        <v>167.71948443155199</v>
-      </c>
-      <c r="F7" s="10">
-        <v>23.866113566664101</v>
+      <c r="C7" s="6">
+        <f t="shared" si="0"/>
+        <v>95.813586086847806</v>
+      </c>
+      <c r="D7" s="6">
+        <f t="shared" si="1"/>
+        <v>191.62717217369561</v>
+      </c>
+      <c r="E7" s="6">
+        <f t="shared" si="2"/>
+        <v>170.223538814634</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="3"/>
+        <v>21.403633359061615</v>
+      </c>
+      <c r="K7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7">
+        <v>80</v>
+      </c>
+      <c r="M7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N7">
+        <v>95.813586086847806</v>
+      </c>
+      <c r="O7">
+        <v>170.223538814634</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="5" t="s">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="10">
-        <v>74.476941686509903</v>
-      </c>
-      <c r="D8" s="10">
-        <v>148.95388337301901</v>
-      </c>
-      <c r="E8" s="10">
-        <v>123.309054600008</v>
-      </c>
-      <c r="F8" s="10">
-        <v>25.644828773011099</v>
+      <c r="C8" s="6">
+        <f t="shared" si="0"/>
+        <v>75.259640783854607</v>
+      </c>
+      <c r="D8" s="6">
+        <f t="shared" si="1"/>
+        <v>150.51928156770921</v>
+      </c>
+      <c r="E8" s="6">
+        <f t="shared" si="2"/>
+        <v>105.588941180324</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="3"/>
+        <v>44.930340387385215</v>
+      </c>
+      <c r="K8">
+        <v>70</v>
+      </c>
+      <c r="L8">
+        <v>80</v>
+      </c>
+      <c r="M8" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8">
+        <v>75.259640783854607</v>
+      </c>
+      <c r="O8">
+        <v>105.588941180324</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
         <v>85</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="10">
-        <v>78.757837013962302</v>
-      </c>
-      <c r="D9" s="10">
-        <v>157.51567402792401</v>
-      </c>
-      <c r="E9" s="10">
-        <v>137.982334393434</v>
-      </c>
-      <c r="F9" s="10">
-        <v>19.533339634490201</v>
+      <c r="C9" s="6">
+        <f t="shared" si="0"/>
+        <v>78.759119500821896</v>
+      </c>
+      <c r="D9" s="6">
+        <f t="shared" si="1"/>
+        <v>157.51823900164379</v>
+      </c>
+      <c r="E9" s="6">
+        <f t="shared" si="2"/>
+        <v>137.98922464330201</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="3"/>
+        <v>19.529014358341783</v>
+      </c>
+      <c r="K9" t="s">
+        <v>13</v>
+      </c>
+      <c r="L9">
+        <v>85</v>
+      </c>
+      <c r="M9" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9">
+        <v>78.759119500821896</v>
+      </c>
+      <c r="O9">
+        <v>137.98922464330201</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="5" t="s">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="10">
-        <v>63.643645421149898</v>
-      </c>
-      <c r="D10" s="10">
-        <v>127.287290842299</v>
-      </c>
-      <c r="E10" s="10">
-        <v>107.008388600053</v>
-      </c>
-      <c r="F10" s="10">
-        <v>20.2789022422469</v>
+      <c r="C10" s="6">
+        <f t="shared" si="0"/>
+        <v>64.152741577659796</v>
+      </c>
+      <c r="D10" s="6">
+        <f t="shared" si="1"/>
+        <v>128.30548315531959</v>
+      </c>
+      <c r="E10" s="6">
+        <f t="shared" si="2"/>
+        <v>94.996412519428006</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="3"/>
+        <v>33.309070635891587</v>
+      </c>
+      <c r="K10">
+        <v>70</v>
+      </c>
+      <c r="L10">
+        <v>85</v>
+      </c>
+      <c r="M10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10">
+        <v>64.152741577659796</v>
+      </c>
+      <c r="O10">
+        <v>94.996412519428006</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
         <v>90</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="10">
-        <v>59.849478033622098</v>
-      </c>
-      <c r="D11" s="10">
-        <v>119.698956067244</v>
-      </c>
-      <c r="E11" s="10">
-        <v>104.977582589055</v>
-      </c>
-      <c r="F11" s="10">
-        <v>14.7213734781888</v>
+      <c r="C11" s="6">
+        <f t="shared" si="0"/>
+        <v>60.009005914026297</v>
+      </c>
+      <c r="D11" s="6">
+        <f t="shared" si="1"/>
+        <v>120.01801182805259</v>
+      </c>
+      <c r="E11" s="6">
+        <f t="shared" si="2"/>
+        <v>103.38753854288601</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="3"/>
+        <v>16.630473285166588</v>
+      </c>
+      <c r="K11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11">
+        <v>90</v>
+      </c>
+      <c r="M11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N11">
+        <v>60.009005914026297</v>
+      </c>
+      <c r="O11">
+        <v>103.38753854288601</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="5" t="s">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="10">
-        <v>47.347254861462098</v>
-      </c>
-      <c r="D12" s="10">
-        <v>94.694509722924295</v>
-      </c>
-      <c r="E12" s="10">
-        <v>80.139188658210699</v>
-      </c>
-      <c r="F12" s="10">
-        <v>14.555321064713601</v>
+      <c r="C12" s="6">
+        <f t="shared" si="0"/>
+        <v>47.806573269934098</v>
+      </c>
+      <c r="D12" s="6">
+        <f t="shared" si="1"/>
+        <v>95.613146539868197</v>
+      </c>
+      <c r="E12" s="6">
+        <f t="shared" si="2"/>
+        <v>71.924926657641606</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="3"/>
+        <v>23.688219882226591</v>
+      </c>
+      <c r="K12">
+        <v>70</v>
+      </c>
+      <c r="L12">
+        <v>90</v>
+      </c>
+      <c r="M12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12">
+        <v>47.806573269934098</v>
+      </c>
+      <c r="O12">
+        <v>71.924926657641606</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
         <v>95</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="10">
-        <v>40.493220043359699</v>
-      </c>
-      <c r="D13" s="10">
-        <v>80.986440086719497</v>
-      </c>
-      <c r="E13" s="10">
-        <v>70.915863875499994</v>
-      </c>
-      <c r="F13" s="10">
-        <v>10.0705762112194</v>
+      <c r="C13" s="6">
+        <f t="shared" si="0"/>
+        <v>40.468914087214301</v>
+      </c>
+      <c r="D13" s="6">
+        <f t="shared" si="1"/>
+        <v>80.937828174428603</v>
+      </c>
+      <c r="E13" s="6">
+        <f t="shared" si="2"/>
+        <v>68.805016737848703</v>
+      </c>
+      <c r="F13" s="6">
+        <f t="shared" si="3"/>
+        <v>12.1328114365799</v>
+      </c>
+      <c r="K13" t="s">
+        <v>13</v>
+      </c>
+      <c r="L13">
+        <v>95</v>
+      </c>
+      <c r="M13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N13">
+        <v>40.468914087214301</v>
+      </c>
+      <c r="O13">
+        <v>68.805016737848703</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="5" t="s">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="10">
-        <v>29.559478410442299</v>
-      </c>
-      <c r="D14" s="10">
-        <v>59.118956820884598</v>
-      </c>
-      <c r="E14" s="10">
-        <v>50.282539458227198</v>
-      </c>
-      <c r="F14" s="10">
-        <v>8.8364173626573397</v>
+      <c r="C14" s="6">
+        <f t="shared" si="0"/>
+        <v>29.6009794217482</v>
+      </c>
+      <c r="D14" s="6">
+        <f t="shared" si="1"/>
+        <v>59.201958843496399</v>
+      </c>
+      <c r="E14" s="6">
+        <f t="shared" si="2"/>
+        <v>45.269301977696301</v>
+      </c>
+      <c r="F14" s="6">
+        <f t="shared" si="3"/>
+        <v>13.932656865800098</v>
+      </c>
+      <c r="K14">
+        <v>70</v>
+      </c>
+      <c r="L14">
+        <v>95</v>
+      </c>
+      <c r="M14" t="s">
+        <v>15</v>
+      </c>
+      <c r="N14">
+        <v>29.6009794217482</v>
+      </c>
+      <c r="O14">
+        <v>45.269301977696301</v>
       </c>
     </row>
   </sheetData>
